--- a/data-manipulation-scripts/sheets-cleanup/sheets/CAPACETE 13_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CAPACETE 13_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -62,6 +62,54 @@
   </si>
   <si>
     <t>CAPACETE VERMELHO SAN MARINO 60</t>
+  </si>
+  <si>
+    <t>7898483640096</t>
+  </si>
+  <si>
+    <t>CAPACETE VERMELHO SAN MARINO 58</t>
+  </si>
+  <si>
+    <t>7898483667635</t>
+  </si>
+  <si>
+    <t>CAPACETE SAN MARINO BRANCO 62</t>
+  </si>
+  <si>
+    <t>7898483640102</t>
+  </si>
+  <si>
+    <t>CAPACETE SAN MARINO VERMELHO 60</t>
+  </si>
+  <si>
+    <t>7898483640164</t>
+  </si>
+  <si>
+    <t>CAPACETE SAN MARINO PRETO FOSCO 60</t>
+  </si>
+  <si>
+    <t>7898483640461</t>
+  </si>
+  <si>
+    <t>CAPACETE SAN MARINO BRANCO 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7898483667581</t>
+  </si>
+  <si>
+    <t>CAPACETE SAN MARINO VERMELHO 62</t>
+  </si>
+  <si>
+    <t>7898483667574</t>
+  </si>
+  <si>
+    <t>CAPACETE  SAN MARINO PRETO 62</t>
+  </si>
+  <si>
+    <t>7898483640034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACETE SAN MARINO PRETO 58 </t>
   </si>
 </sst>
 </file>
@@ -367,7 +415,9 @@
       <c r="C2" s="2">
         <v>2.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -379,7 +429,9 @@
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
@@ -389,7 +441,9 @@
       <c r="C4" s="2">
         <v>2.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -399,7 +453,9 @@
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3"/>
@@ -409,7 +465,9 @@
       <c r="C6" s="2">
         <v>2.0</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3"/>
@@ -419,7 +477,9 @@
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3"/>
@@ -427,9 +487,11 @@
         <v>12</v>
       </c>
       <c r="C8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>3.0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3"/>
@@ -439,7 +501,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
@@ -449,7 +513,9 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -461,55 +527,121 @@
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="A19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>220.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3"/>
